--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-full-2.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-full-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6093DFCA-FD89-42E0-908A-5CCF9782E60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D44C50B-1DCE-4ECA-BB05-1FABEC940DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{EBB83224-786A-4651-8A9C-70774A502AC5}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{73229005-B243-431B-9101-0227F2523BB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="111" r:id="rId3"/>
+    <pivotCache cacheId="143" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576885185183" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{C4FAD698-5F82-4BA5-9F0D-860394B901E8}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579457523148" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{EE62F67A-0E25-4EFD-AD26-3309EBA133EF}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C6A3C76B-0239-4FA3-8738-5B32FCBCBE2E}" name="AllErrorPivot" cacheId="111" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05F76C3B-F75B-4F78-A4BB-F5AF25FA6077}" name="AllErrorPivot" cacheId="143" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -570,7 +570,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B526DA3B-43BB-4A94-BF11-89201BB75767}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC8E6CA-2B64-47BF-9AF9-563D9D32AE96}">
   <dimension ref="A4:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -616,7 +616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E36238D-D550-4D77-9D4D-2CE1A534FC08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED0319F-5BB2-4EC5-9DED-7F20359489D2}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
